--- a/Theory.xlsx
+++ b/Theory.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_June_22\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_June_22\project1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4E3927-1AF6-4687-ADE8-1AF1E865ACF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAC3300-D973-47A0-8EBD-023D553EA16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{28229DAC-A180-4F0F-87B8-08E9AB6A9375}"/>
   </bookViews>
@@ -33,15 +33,107 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+  <si>
+    <t>Initially</t>
+  </si>
+  <si>
+    <t>Commits</t>
+  </si>
+  <si>
+    <t>Zomato app</t>
+  </si>
+  <si>
+    <t>Sort by delivery time</t>
+  </si>
+  <si>
+    <t>Dev1</t>
+  </si>
+  <si>
+    <t>Pull</t>
+  </si>
+  <si>
+    <t>Dev2</t>
+  </si>
+  <si>
+    <t>Dev3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pull </t>
+  </si>
+  <si>
+    <t>fetch + merge</t>
+  </si>
+  <si>
+    <t>git clone : Starts from Remote to Local/Desktop</t>
+  </si>
+  <si>
+    <t>git init,add,commit,push: Starts from Local to Remote</t>
+  </si>
+  <si>
+    <t>OSS</t>
+  </si>
+  <si>
+    <t>pandas</t>
+  </si>
+  <si>
+    <t>1. fork</t>
+  </si>
+  <si>
+    <t>2. clone</t>
+  </si>
+  <si>
+    <t>3. edit, test</t>
+  </si>
+  <si>
+    <t>4. PR - pull request</t>
+  </si>
+  <si>
+    <t>local</t>
+  </si>
+  <si>
+    <t>modified fi1</t>
+  </si>
+  <si>
+    <t>remote</t>
+  </si>
+  <si>
+    <t>original f1</t>
+  </si>
+  <si>
+    <t>rebase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add </t>
+  </si>
+  <si>
+    <t>commit</t>
+  </si>
+  <si>
+    <t>push to main</t>
+  </si>
+  <si>
+    <t>switch to feature</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -64,8 +156,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -623,6 +716,754 @@
           <a:endParaRPr lang="en-IN" sz="1100"/>
         </a:p>
         <a:p>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Rectangle 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{448DC0CC-43A7-0B7A-9F6C-2E903CB2DB2B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1905000" y="9855200"/>
+          <a:ext cx="4292600" cy="1676400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>454025</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>149225</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A01D4B0-F3A8-86C0-44F5-82E1E3B80FE9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2282825" y="10020300"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>User 1/repo3</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="TextBox 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A3D9B96-DDD7-0F97-898F-8BA164FE1F0C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3759200" y="10083800"/>
+          <a:ext cx="1003300" cy="869950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>Your github</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>Fork</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>Copy</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t> of user1/repo3</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>241300</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>539750</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="TextBox 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0280CA0-EF74-39B6-0D54-79BE0DFF728B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5118100" y="10147300"/>
+          <a:ext cx="908050" cy="787400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>clone to local</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>107950</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Rectangle 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB5EF22F-5FFB-3976-66F4-AADFAA9AC962}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1936750" y="12153900"/>
+          <a:ext cx="4368800" cy="3067050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Rectangle 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F6DE8E2-4929-54AA-93DD-A79575F13808}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5276850" y="12319000"/>
+          <a:ext cx="946150" cy="1752600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>406400</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>546100</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="TextBox 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B862103-E7C5-A3F2-D571-53C7B9FBFDD1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5283200" y="12534900"/>
+          <a:ext cx="749300" cy="1276350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>Remote  project repo</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>Original user's</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t> profile</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>273050</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Rectangle 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E68C6F96-4BA3-B76C-034D-E63D80468987}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2266950" y="12369800"/>
+          <a:ext cx="1054100" cy="774700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>431800</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="Rectangle 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{018710C5-F071-DA6F-DF37-862F4F7DD846}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2260600" y="13519150"/>
+          <a:ext cx="1263650" cy="908050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>107950</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="TextBox 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53FFBF1B-D320-7A86-7965-C27A87DB8835}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2463800" y="12471400"/>
+          <a:ext cx="692150" cy="546100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>Dev1 local</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>44450</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="TextBox 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C33F23F8-F0C9-95BC-A5A9-C87AADB402BC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2482850" y="13671550"/>
+          <a:ext cx="749300" cy="546100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>Dev2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t> local</a:t>
+          </a:r>
           <a:endParaRPr lang="en-IN" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -929,9 +1770,150 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D244690-24BE-427E-945E-87DC4EE9CADC}">
-  <dimension ref="A1"/>
+  <dimension ref="C34:G135"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <sheetData>
+    <row r="34" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D34" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D35">
+        <v>5000</v>
+      </c>
+      <c r="E35" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D36" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D37">
+        <v>7000</v>
+      </c>
+      <c r="E37" t="s">
+        <v>3</v>
+      </c>
+      <c r="G37" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D46" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="4:4" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="D49" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="4:4" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="D50" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E88" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E89" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E90" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="91" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E91" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E92" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E93" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="125" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C125" t="s">
+        <v>18</v>
+      </c>
+      <c r="F125" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="126" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C126" t="s">
+        <v>19</v>
+      </c>
+      <c r="F126" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="128" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="E128" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="131" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C131" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="132" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C132" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="133" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C133" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="134" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C134" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="135" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C135" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Theory.xlsx
+++ b/Theory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_June_22\project1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAC3300-D973-47A0-8EBD-023D553EA16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B587225-6FD4-4DE6-851A-86E18B07BBC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{28229DAC-A180-4F0F-87B8-08E9AB6A9375}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>Initially</t>
   </si>
@@ -115,13 +115,61 @@
   </si>
   <si>
     <t>switch to feature</t>
+  </si>
+  <si>
+    <t>main</t>
+  </si>
+  <si>
+    <t>fea1</t>
+  </si>
+  <si>
+    <t>Rebase</t>
+  </si>
+  <si>
+    <t>Main</t>
+  </si>
+  <si>
+    <t>file1</t>
+  </si>
+  <si>
+    <t>line 5</t>
+  </si>
+  <si>
+    <t>some code</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>some other code</t>
+  </si>
+  <si>
+    <t>PR &amp; merge</t>
+  </si>
+  <si>
+    <t>git  checkout main</t>
+  </si>
+  <si>
+    <t>merge main - feature1</t>
+  </si>
+  <si>
+    <t>push to remote</t>
+  </si>
+  <si>
+    <t>changes in feature1</t>
+  </si>
+  <si>
+    <t>personal project</t>
+  </si>
+  <si>
+    <t>prod project</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,6 +182,12 @@
       <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1463,6 +1517,300 @@
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
             <a:t> local</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>137</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="Oval 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7389BCA5-59A2-39E7-CFD5-F8D4585C1C47}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5562600" y="24168100"/>
+          <a:ext cx="1238250" cy="1136650"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>317500</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="TextBox 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6E7C494-1991-B0DB-7500-223651CC24B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5803900" y="24377650"/>
+          <a:ext cx="768350" cy="1098550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>main</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>file1</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>modified f1</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>215900</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="Oval 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05273A40-01A2-2505-D0E2-B54377EBD766}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5702300" y="25628600"/>
+          <a:ext cx="1377950" cy="1447800"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>469900</xdr:colOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="TextBox 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10B813FF-720D-2E0E-335E-A6825B9414E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5956300" y="25933400"/>
+          <a:ext cx="889000" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>feature 1</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>file1</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>modified</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t> f1</a:t>
           </a:r>
           <a:endParaRPr lang="en-IN" sz="1100"/>
         </a:p>
@@ -1770,7 +2118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D244690-24BE-427E-945E-87DC4EE9CADC}">
-  <dimension ref="C34:G135"/>
+  <dimension ref="B34:L135"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="34" spans="4:7" x14ac:dyDescent="0.35">
@@ -1867,7 +2215,75 @@
         <v>17</v>
       </c>
     </row>
-    <row r="125" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D102" t="s">
+        <v>29</v>
+      </c>
+      <c r="L102" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="103" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="L103" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="104" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="L104" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="105" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D105" t="s">
+        <v>30</v>
+      </c>
+      <c r="L105" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="106" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D106" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="107" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D107" t="s">
+        <v>32</v>
+      </c>
+      <c r="E107" t="s">
+        <v>33</v>
+      </c>
+      <c r="L107" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="108" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="H108" t="s">
+        <v>36</v>
+      </c>
+      <c r="L108" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="109" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D109" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="110" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D110" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="111" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D111" t="s">
+        <v>32</v>
+      </c>
+      <c r="E111" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="125" spans="2:6" x14ac:dyDescent="0.35">
       <c r="C125" t="s">
         <v>18</v>
       </c>
@@ -1875,7 +2291,10 @@
         <v>20</v>
       </c>
     </row>
-    <row r="126" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B126" t="s">
+        <v>27</v>
+      </c>
       <c r="C126" t="s">
         <v>19</v>
       </c>
@@ -1883,7 +2302,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="128" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B127" t="s">
+        <v>28</v>
+      </c>
+      <c r="C127" t="s">
+        <v>19</v>
+      </c>
+      <c r="F127" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="128" spans="2:6" x14ac:dyDescent="0.35">
       <c r="E128" t="s">
         <v>22</v>
       </c>
@@ -1914,6 +2344,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
